--- a/home/blog.xlsx
+++ b/home/blog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C6B236-891F-45F6-9104-4A024CDD344C}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B75CCA3-3B63-4336-A2DE-F16B8D74EE5D}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="6" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
   </bookViews>
   <sheets>
     <sheet name="config_tabs" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="160">
   <si>
     <t>tab_key</t>
   </si>
@@ -159,16 +159,585 @@
   </si>
   <si>
     <t>allow_comments</t>
+  </si>
+  <si>
+    <t># Regras da Liga de Fantasy Basketball
+Liga de Fantasy Basketball em formato keeper, no qual os times se mantêm ao final de uma temporada, permanecendo o mesmo elenco por vários anos, podendo ser alterado apenas por dispensas, trocas, draft e contratações de Free Agents. São 14 times se enfrentando em 39 jogos na regular season, e os 8 primeiros se classificam para os playoffs.
+## 0. Configurações Gerais
+- Neste fantasy, você monta o seu elenco inicial através de um draft de balizamento, realizado na temporada de abertura da liga.
+- Durante a temporada, em cada semana de jogos, você escala o seu time com 6 titulares, sendo um de cada posição (PG, SG, SF, PF e C) e um 6th man, que pode ser de qualquer posição.
+- Além dos titulares, escala-se 6 reservas, sendo um de cada posição e um 6th man.
+- Em cada semana, todas as equipes enfrentam outros 3 times.
+- Os critérios utilizados nos jogos serão os números produzidos pelos jogadores durante a semana na NBA: pontos, assistências, rebotes, steals, blocks, bolas de 3 e turnovers.
+- A soma dos resultados obtidos pelos titulares em cada quesito será a pontuação final do time.
+- Vence o jogo o time que vencer o maior número desses 7 quesitos.
+- Os critérios de desempate serão, nesta ordem: maior eficiência naquele jogo, mais pontos, mais rebotes e assim sucessivamente. Em caso de empate em todos os critérios, haverá sorteio.
+- É obrigatória a escalação semanal de todos os times. Cada GM deve postar sua escalação no tópico de escalações do VK.
+- Se o jogador escalado não entrar em quadra por qualquer motivo, será utilizado um reserva da mesma posição.
+- A escalação poderá ser feita até 1 hora antes do início das partidas de cada semana.
+- Caso o GM não envie a escalação, será utilizada a escalação da semana anterior.
+- Duas semanas sem envio não justificado geram notificação ao GM. Em caso de repetição, haverá WO.
+## 1. Elenco
+- Ao início da temporada regular, cada elenco do time principal deve conter entre 12 e 15 jogadores.
+- O elenco da D-League deve conter entre 0 e 5 jogadores.
+- O elenco principal deve ter pelo menos 2 jogadores de cada posição: PG, SG, SF, PF e C.
+- Na D-League não existem restrições sobre posições, porém esses jogadores não contam para o elenco principal.
+- A quantidade de jogadores no elenco principal não precisa ser respeitada durante os períodos de intertemporada.
+- Nos períodos sem jogos, os times podem ultrapassar os limites de salário e de número de jogadores, mas devem voltar à regularidade até a data limite de 7 dias antes do início da nova temporada.
+- O elenco da D-League nunca pode ultrapassar o teto salarial da D-League.
+- A não adequação antes da temporada regular, ou a permanência fora das regras durante a temporada, por falta ou excesso de jogadores ou por falta de cap space, implica em derrotas por WO durante a semana em que o time estiver irregular.
+- Em caso de persistência por múltiplas semanas, o GM com excesso de jogadores terá um contrato selecionado pela gerência da liga para dispensa.
+- Já o GM com jogador a menos continuará sofrendo WO e poderá receber um jogador de salário mínimo escolhido pela liga.
+## 2. Salários, Contratos e Dispensas
+- O teto salarial do time principal será fixo em $110,000,000.
+- O teto salarial do elenco da D-League será de $14,000,000.
+### Team Option
+- No ano em que o jogador tiver Team Option, a equipe poderá optar por continuar ou não com esse jogador.
+- Caso decida liberá-lo, não haverá multa para a equipe.
+- O jogador se tornará Free Agent irrestrito.
+- O GM poderá tentar contratar esse mesmo jogador através do leilão.
+- Se o GM não responder o tópico de Team Option dentro do prazo, o jogador será desligado do time automaticamente.
+### 2.1 Dispensas
+- O número de dispensas é ilimitado.
+- Se o jogador for dispensado durante a temporada regular, ele só poderá voltar para a mesma equipe na temporada regular seguinte.
+- Se o jogador for dispensado durante a intertemporada, ele só poderá voltar para a antiga equipe na intertemporada seguinte.
+- Se após uma dispensa o time ficar fora das normas de teto salarial e de número de jogadores no elenco, a equipe terá 24 horas para se readequar.
+- Caso contrário, a readequação será feita pela gerência da liga.
+### 2.2 Multas
+- Entre $500,000 e $5,000,000, a multa será de 15% do salário anual em cada ano de contrato.
+- Entre $5,000,001 e $10,000,000, a multa será de 20% do salário anual em cada ano de contrato.
+- Entre $10,000,001 e $15,000,000, a multa será de 25% do salário anual em cada ano de contrato.
+- A partir de $15,000,001, a multa será de 30% do salário anual em cada ano de contrato.
+- Se o jogador possuir valores diferentes em seu contrato, cada multa será calculada separadamente em cada ano.
+- As multas acumuladas durante a temporada serão descontadas no espaço disponível para ofertas nos leilões de intertemporada.
+- Essas multas não têm efeito durante a temporada regular.
+### 2.3 Anistia
+- Anistia consiste na dispensa do jogador com perdão dos dividendos salariais, ou seja, o jogador é dispensado e a equipe não paga multa.
+- Cada equipe poderá anistiar 1 jogador de seu elenco.
+- Esse jogador se tornará UFA.
+- Se o jogador for anistiado durante a temporada regular, ele só poderá voltar para a antiga equipe na próxima temporada regular.
+- Se o jogador for anistiado durante a intertemporada, ele só poderá voltar para a antiga equipe na intertemporada seguinte.
+- A anistia poderá ser feita apenas 1 vez dentro de um período de 5 temporadas.
+## 3. Trocas de Jogadores e Picks
+- As trocas podem envolver jogadores e picks de draft.
+- Cada GM envolvido na troca deverá confirmá-la no tópico de trocas.
+- Após todas as confirmações, a troca é efetivada.
+- Se o jogador for trocado durante a temporada regular, ele só poderá voltar para a antiga equipe na próxima temporada regular.
+- Se o jogador for trocado durante a intertemporada, ele só poderá voltar para a antiga equipe na próxima intertemporada.
+- Se durante a temporada regular o time ultrapassar o cap ou o limite de jogadores após uma troca, a equipe terá 24 horas para se readequar.
+- Caso contrário, a readequação será feita pela gerência da liga.
+- Se uma equipe violar as regras das picks, a troca será invalidada até que os GMs acertem um acordo válido.
+- Ao início dos playoffs, estarão proibidas trocas até o fim da pós-temporada.
+## 4. Draft de Rookies e Picks
+- Cada equipe tem 2 escolhas de draft por temporada: uma de 1ª rodada e uma de 2ª rodada.
+- Uma equipe deverá escolher ao menos 1 jogador a cada 2 anos no primeiro round do draft.
+- O sorteio das picks ocorre com base na classificação final da temporada.
+- Cada contrato de rookie terá 2 anos garantidos e 2 anos de Team Option.
+- O salário dos rookies será pré-fixado conforme a rookie scale abaixo.
+| Pick | Ano 1 | Ano 2 | Ano 3 | Ano 4 |
+|------|------:|------:|------:|------:|
+| 1st pick | $9,000,000 | $9,500,000 | $10,500,000 | $11,500,000 |
+| 2nd pick | $8,000,000 | $8,500,000 | $9,250,000 | $10,000,000 |
+| 3rd pick | $7,000,000 | $7,500,000 | $8,250,000 | $9,000,000 |
+| 4th pick | $6,000,000 | $6,500,000 | $7,000,000 | $7,500,000 |
+| 5th pick | $5,000,000 | $5,500,000 | $6,000,000 | $6,500,000 |
+| 6th pick | $4,500,000 | $5,000,000 | $5,500,000 | $6,000,000 |
+| 7th pick | $4,000,000 | $4,500,000 | $5,000,000 | $5,500,000 |
+- A partir da 8th pick, cada pick diminuirá em $200,000 no salário do primeiro ano em relação à pick anterior.
+| Pick | Ano 1 | Ano 2 | Ano 3 | Ano 4 |
+|------|------:|------:|------:|------:|
+| 8th pick | $3,800,000 | $4,000,000 | $4,200,000 | $4,500,000 |
+| 9th pick | $3,600,000 | $3,800,000 | $4,000,000 | $4,300,000 |
+| 10th pick | $3,400,000 | $3,600,000 | $3,800,000 | $4,100,000 |
+- Todas as picks de 2nd round terão salários de $1,000,000 nos 4 anos de contrato.
+## 5. Leilão de Free Agents e Mudança de Posições
+### 5.1 Leilão de Temporada Regular
+- Durante a temporada regular do fantasy, jogadores sem time poderão ser contratados com contratos até o fim da temporada.
+- As ofertas deverão ser enviadas entre segunda e quinta-feira via e-mail, VK ou WhatsApp para o GM do fantasy.
+- Os resultados serão divulgados em até 24 horas após o fim das propostas.
+### 5.1.1 Requisitos para a equipe
+- A equipe deve ter ao menos 1 espaço vago no elenco para cada proposta enviada, antes do envio.
+- Deve ter espaço salarial suficiente para acomodar o valor proposto.
+- Deve propor contrato de no máximo 1 temporada.
+- A proposta mínima deve ser de $1,000,000 e a máxima de $40,000,000.
+### 5.1.2 Critérios do leilão
+- O leilão é feito às cegas.
+- O leilão se inicia a partir da segunda semana da temporada regular e vai até a penúltima semana.
+- O time com a maior proposta salarial ficará com o jogador.
+- Se 2 times enviarem a mesma melhor oferta, os empatados terão 24 horas para enviar nova proposta.
+- Em caso de novo empate, abre-se novo período de 24 horas, e assim sucessivamente.
+- Se nesse período nenhuma das equipes empatadas enviar nova proposta, o jogador volta para a lista de jogadores sem time.
+### 5.2 Leilões de Offseason
+- Ao fim de cada temporada, alguns jogadores terão seus contratos encerrados e virarão Free Agents restritos.
+- O antigo time terá a palavra final para igualar a oferta ou não.
+- A proposta do time que possuía o jogador antes de ele virar Free Agent não conta para o limite salarial do leilão.
+- O valor disponível para contratar no leilão será o teto salarial disponível naquele ano, descontadas multas acumuladas e contratos já assinados.
+- Cada time poderá contratar até 10 jogadores no leilão.
+- O tempo de contrato é de 1 a 4 temporadas.
+- Casos de renovação não contam dentro do limite de 10 contratações.
+- Somente em casos de renovação a equipe poderá passar do limite do cap, devendo se readequar antes do início da temporada seguinte.
+- O valor mínimo para lances no leilão é $1,000,000.
+- Se durante 24 horas não houver novas propostas pelo jogador, ele assinará com a equipe da proposta atual.
+- Se algum GM oferecer o contrato máximo, 40% do teto salarial da liga, isto é, $44,000,000, o jogador fica em definitivo na equipe.
+### 5.3 Lances nos Leilões de Offseason
+- Oferta máxima que qualquer jogador pode receber: $44,000,000.
+- Oferta mínima que qualquer jogador pode receber: $1,000,000.
+- Ofertas entre $1,000,000 e $3,000,000 devem ter 1 a 3 anos de duração.
+- Ofertas entre $3,100,000 e $9,900,000 devem ter de 1 a 4 anos de duração.
+- Ofertas entre $10,000,000 e $19,900,000 devem ter duração mínima de 2 anos.
+- Ofertas a partir de $20,000,000 devem ter 3 ou 4 anos de duração.
+- As ofertas devem ser maiores que a anterior em múltiplos inteiros de $500,000.
+## 5.4 Mudança de Posições
+- Se o jogador atuou 30% da última temporada em determinada posição, com base no Basketball Reference, ele poderá jogar naquela posição.
+- Ao final de cada temporada, será disponibilizada uma lista com os jogadores que poderão modificar a posição.
+- Serão aceitas propostas de adequação da lista, desde que estejam de acordo com a referência utilizada.
+## 6. D-League
+- As equipes poderão manter parte de seus jogadores na D-League respeitando as condições abaixo.
+- Somente jogadores que ainda não finalizaram sua 3ª temporada na NBA podem ficar na D-League.
+- O elenco da D-League pode ter de 0 a 5 jogadores.
+- O teto salarial da D-League será de $14,000,000.
+- A qualquer momento na temporada, o GM poderá enviar jogadores da D-League para o elenco principal e vice-versa, desde que haja vagas e espaço na folha salarial.
+- Os jogadores da D-League poderão ser envolvidos livremente em trades.
+- Jogadores movidos para a D-League após a segunda-feira só terão efeito a partir da quinta-feira, para evitar conflito com propostas do leilão.
+- Não há regras sobre posições na D-League.
+## 7. Escalação
+A escalação de cada time é válida para 3 jogos por semana, sem poder sofrer alterações, e deve ter a seguinte estrutura:
+### Titulares
+- PG
+- SG
+- SF
+- PF
+- C
+- 6th Man
+### Reservas
+- PG
+- SG
+- SF
+- PF
+- C
+- 6th Man
+- O 6th man pode ser um jogador de qualquer posição.
+- Cada jogador pode estar em no máximo 2 posições considerando titulares e reservas.
+- Na escalação titular não pode haver repetições.
+- Se o time na NBA jogar 2 vezes na semana, as stats do jogo 2 se repetem no jogo 3.
+- Se o time na NBA jogar 1 vez na semana, as stats se repetem nas 3 partidas do fantasy.
+- Se o time na NBA não jogar durante a semana, o jogador escalado ficará de fora e entrará o reserva.
+## 8. Classificação e Playoffs
+- 14 times jogam todos contra todos 3 vezes, totalizando 39 jogos.
+- Os 8 primeiros se classificam aos playoffs.
+- As séries serão melhor de 5 jogos até a final.
+- Cada fase dos playoffs começará numa data específica, e os jogos usados para contagem dos critérios serão os 5 primeiros jogos de cada time da NBA dentro daquele período.
+- A final será dividida em 2 semanas, a primeira com 3 jogos e a segunda com 2 jogos, com possibilidade de mudança de escalação para a segunda semana.
+### Quartas de final
+- [A] Primeiro x Oitavo
+- [B] Segundo x Sétimo
+- [C] Terceiro x Sexto
+- [D] Quarto x Quinto
+### Semifinais
+- [E] Vencedor de A x Vencedor de D
+- [F] Vencedor de B x Vencedor de C
+### Final da Liga
+- Vencedor de E x Vencedor de F
+### Critérios de desempate na classificação da regular season
+**Empate entre 2 times**
+- Confronto direto.
+- Média de eficiência na temporada.
+- Número de vitórias contra os times do top 8.
+- Número de quesitos vencidos na temporada.
+- Sorteio.
+**Empate entre 3 ou mais times**
+- Número de vitórias nos confrontos envolvendo os times empatados.
+- Média de eficiência na temporada.
+- Número de vitórias contra os times do top 8.
+- Número de quesitos vencidos na temporada.
+- Sorteio.</t>
+  </si>
+  <si>
+    <t>r1</t>
+  </si>
+  <si>
+    <t>Regras 2026-27</t>
+  </si>
+  <si>
+    <t>Filipe</t>
+  </si>
+  <si>
+    <t>e1t2627</t>
+  </si>
+  <si>
+    <t>e2t2627</t>
+  </si>
+  <si>
+    <t>e3t2627</t>
+  </si>
+  <si>
+    <t>e4t2627</t>
+  </si>
+  <si>
+    <t>e5t2627</t>
+  </si>
+  <si>
+    <t>e6t2627</t>
+  </si>
+  <si>
+    <t>e7t2627</t>
+  </si>
+  <si>
+    <t>Mudanca de Posicoes</t>
+  </si>
+  <si>
+    <t>Team Option</t>
+  </si>
+  <si>
+    <t>Mudanca de Regras</t>
+  </si>
+  <si>
+    <t>Votacao de Regras</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Inicio da temporada</t>
+  </si>
+  <si>
+    <t>Playoffs</t>
+  </si>
+  <si>
+    <t>e8t2627</t>
+  </si>
+  <si>
+    <t>Realizado</t>
+  </si>
+  <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
+    <t>Aguardando</t>
+  </si>
+  <si>
+    <t>Depende do calendario oficial</t>
+  </si>
+  <si>
+    <t>26-27</t>
+  </si>
+  <si>
+    <t>Contratos</t>
+  </si>
+  <si>
+    <t>Regras</t>
+  </si>
+  <si>
+    <t>Leilao</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>Fim das trocas</t>
+  </si>
+  <si>
+    <t>Trocas</t>
+  </si>
+  <si>
+    <t>Três semanas antes do fim da temporada</t>
+  </si>
+  <si>
+    <t>e9t2627</t>
+  </si>
+  <si>
+    <t>e10t2627</t>
+  </si>
+  <si>
+    <t>Três semanas depois do inicio da temporada</t>
+  </si>
+  <si>
+    <t>jogos</t>
+  </si>
+  <si>
+    <t>links</t>
+  </si>
+  <si>
+    <t>l01</t>
+  </si>
+  <si>
+    <t>l02</t>
+  </si>
+  <si>
+    <t>l03</t>
+  </si>
+  <si>
+    <t>l04</t>
+  </si>
+  <si>
+    <t>l05</t>
+  </si>
+  <si>
+    <t>l06</t>
+  </si>
+  <si>
+    <t>l07</t>
+  </si>
+  <si>
+    <t>l08</t>
+  </si>
+  <si>
+    <t>l09</t>
+  </si>
+  <si>
+    <t>l10</t>
+  </si>
+  <si>
+    <t>l11</t>
+  </si>
+  <si>
+    <t>l12</t>
+  </si>
+  <si>
+    <t>l13</t>
+  </si>
+  <si>
+    <t>l14</t>
+  </si>
+  <si>
+    <t>l15</t>
+  </si>
+  <si>
+    <t>l16</t>
+  </si>
+  <si>
+    <t>l17</t>
+  </si>
+  <si>
+    <t>https://keepernba.streamlit.app/</t>
+  </si>
+  <si>
+    <t>pagina</t>
+  </si>
+  <si>
+    <t>página do fantasy</t>
+  </si>
+  <si>
+    <t>Padrão</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1KqIYAMizS7WNIbJXo6Lrle0lDWP1gvjPOEvm-KSj_5M/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Escalacao Padrão - Para todos editarem suas escalacoes semanalmente</t>
+  </si>
+  <si>
+    <t>Pre Season 1</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1PKz9jPsnkaemsrcfa4MAVxdS2FSvLZy3C-KhyeQkM0U/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Jogo 1 da Preseason</t>
+  </si>
+  <si>
+    <t>Jogo 2 da Preseason</t>
+  </si>
+  <si>
+    <t>Pre Season 2</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1RXlz9Xob-9LLEDgAIwHjMysaYpanNqit7m-Dh2BuxJs/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Jogo 1 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 2 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 3 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 4 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 5 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 6 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 7 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 8 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 9 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 10 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 11 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 12 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 13 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/18W8lv2YB4l5fTdtlZ4XRlFRazdmTumJMDwXXly_tpTg/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1wRaVHoT9s8wOav-gKqMe1DTkknb_4cthJj4RKU2HoaM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/18SwibH99E_Crb-pKSWfmjg0mRb9sRq8bRUjoyC0UPzU/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1VOT_9qme4yOtUn7gTMuXD5gUZIyFteDE44ro2pHLVFg/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1yrxI0tprMeHsfenGTb4k634T8J3hqh9mM6X3BS_Jp1w/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1O-DBGgH97ML9R0VZsJ-g1n8InDWd_s6e36CosxYQX1M/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1JLcZ-ulfMhjZ2dxuV49HGsCkSK77LoijaPvdFldI2Fw/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1Mi_0bBQN-r3vR3cNnVos3dZolLINHXZ5-SyI_v-m8zA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1k1nsW_OTJLcub2uI96PFD2NS6iaXF0tUpQeF9Q28YEo/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1IbvR62VxxjKDJplVXwtQJ5ctFSg0-j_YldA72NvEei0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1RRwvkrBm8WkBq9jYe1RkUfyCKkTkMa_Eps7NpdtmKzc/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/17H6QAxOUbGdGnFk39oSecTgNeuI_pYYu1MMI1ubQ9PI/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1PbO2jV6lLXgEH53PqUiZFjxOtayMbdYNTCmisdc7NhM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>A.J. Dybantsa</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>Cameron Boozer</t>
+  </si>
+  <si>
+    <t>Darryn Peterson</t>
+  </si>
+  <si>
+    <t>Darius Acuff</t>
+  </si>
+  <si>
+    <t>Kingston Flemings</t>
+  </si>
+  <si>
+    <t>Mikel Brown Jr.</t>
+  </si>
+  <si>
+    <t>Hannes Steinbach</t>
+  </si>
+  <si>
+    <t>Keaton Wagler</t>
+  </si>
+  <si>
+    <t>Morez Johnson Jr.</t>
+  </si>
+  <si>
+    <t>Brayden Burries</t>
+  </si>
+  <si>
+    <t>Aday Mara</t>
+  </si>
+  <si>
+    <t>Yaxel Lendeborg</t>
+  </si>
+  <si>
+    <t>Cameron Carr</t>
+  </si>
+  <si>
+    <t>Nate Ament</t>
+  </si>
+  <si>
+    <t>Daylin Swain</t>
+  </si>
+  <si>
+    <t>Ebuka Okorie</t>
+  </si>
+  <si>
+    <t>Allen Graves</t>
+  </si>
+  <si>
+    <t>Labaron Phillon</t>
+  </si>
+  <si>
+    <t>Meleek Thomas</t>
+  </si>
+  <si>
+    <t>Bruce Thornton</t>
+  </si>
+  <si>
+    <t>Henry Veesar</t>
+  </si>
+  <si>
+    <t>Sergio De Larrea</t>
+  </si>
+  <si>
+    <t>Bennett Stirtz</t>
+  </si>
+  <si>
+    <t>Chris Cenac Jr.</t>
+  </si>
+  <si>
+    <t>Zuby Ejiofor</t>
+  </si>
+  <si>
+    <t>Christian Anderson Jr.</t>
+  </si>
+  <si>
+    <t>Karim López</t>
+  </si>
+  <si>
+    <t>Drafted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,13 +760,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -211,6 +787,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B9A42A-589F-4B50-8669-074FEDFFFE7B}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -590,6 +1170,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46220</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -597,8 +1200,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88D0B85-D984-4D19-B675-7655ADC2E635}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -626,14 +1234,248 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46157</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46158</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46188</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46204</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46223</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46249</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46401</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46328</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46384</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46384</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46384</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46405</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46436</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84E0651-47D6-4C27-8279-ADF7176CE05C}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +1486,7 @@
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
     <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -678,6 +1520,818 @@
       </c>
       <c r="J1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2">
+        <v>417</v>
+      </c>
+      <c r="I2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3">
+        <v>418</v>
+      </c>
+      <c r="I3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4">
+        <v>419</v>
+      </c>
+      <c r="I4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5">
+        <v>420</v>
+      </c>
+      <c r="I5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6">
+        <v>421</v>
+      </c>
+      <c r="I6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7">
+        <v>422</v>
+      </c>
+      <c r="I7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8">
+        <v>423</v>
+      </c>
+      <c r="I8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9">
+        <v>424</v>
+      </c>
+      <c r="I9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10">
+        <v>425</v>
+      </c>
+      <c r="I10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11">
+        <v>426</v>
+      </c>
+      <c r="I11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12">
+        <v>427</v>
+      </c>
+      <c r="I12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13">
+        <v>428</v>
+      </c>
+      <c r="I13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14">
+        <v>429</v>
+      </c>
+      <c r="I14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>144</v>
+      </c>
+      <c r="H15">
+        <v>430</v>
+      </c>
+      <c r="I15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16">
+        <v>431</v>
+      </c>
+      <c r="I16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17">
+        <v>432</v>
+      </c>
+      <c r="I17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18">
+        <v>433</v>
+      </c>
+      <c r="I18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19">
+        <v>434</v>
+      </c>
+      <c r="I19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20">
+        <v>435</v>
+      </c>
+      <c r="I20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21">
+        <v>436</v>
+      </c>
+      <c r="I21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22">
+        <v>437</v>
+      </c>
+      <c r="I22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23">
+        <v>438</v>
+      </c>
+      <c r="I23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24">
+        <v>439</v>
+      </c>
+      <c r="I24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25">
+        <v>440</v>
+      </c>
+      <c r="I25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26">
+        <v>441</v>
+      </c>
+      <c r="I26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27">
+        <v>442</v>
+      </c>
+      <c r="I27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28">
+        <v>443</v>
+      </c>
+      <c r="I28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29">
+        <v>444</v>
+      </c>
+      <c r="I29" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -687,9 +2341,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CCF4C6-E00D-4D0E-AC8F-5C36E1B21F35}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -716,8 +2372,420 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{D61EF50B-4C43-4162-BD20-9054571CE03F}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{1AA19000-A973-40D3-B160-9F4C454BA7BB}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{AA736724-C129-48E7-8A87-525D908E636E}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{8B10550E-32EE-48CD-ADF4-01162CF1ED0A}"/>
+    <hyperlink ref="D18" r:id="rId5" xr:uid="{8D5DF31B-2F19-47C6-AB9C-F8070017BA6E}"/>
+    <hyperlink ref="D17" r:id="rId6" xr:uid="{4F8A4F6D-D241-46EE-9657-978B55F724BE}"/>
+    <hyperlink ref="D16" r:id="rId7" xr:uid="{EF00FB91-201B-44FF-840F-20A8B8CBA11C}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{5C48C246-1A04-45F7-8463-B57B0697266F}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{BF4358BF-A78C-4BDA-B97C-A221B624B2BA}"/>
+    <hyperlink ref="D13" r:id="rId10" xr:uid="{933A162F-8C8F-4D2C-A06B-38E976979870}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{DA80FD7E-54B4-4FBA-925A-0A9237FCC767}"/>
+    <hyperlink ref="D11" r:id="rId12" xr:uid="{3C5819DB-8592-4354-8E80-B0F350F85237}"/>
+    <hyperlink ref="D9" r:id="rId13" xr:uid="{39BFEB7B-51AB-4E9C-8DF8-75C45DD71C52}"/>
+    <hyperlink ref="D8" r:id="rId14" xr:uid="{53C03D4F-F0CB-4079-8057-D8AB5F62729D}"/>
+    <hyperlink ref="D7" r:id="rId15" xr:uid="{6ACFD238-5286-4E11-89FA-350E104B7DD2}"/>
+    <hyperlink ref="D6" r:id="rId16" xr:uid="{0CA085F1-2C0B-4103-8922-39FC61C77FDB}"/>
+    <hyperlink ref="D10" r:id="rId17" xr:uid="{F512397F-5E3F-4041-9AF2-E3F1A00E1CAF}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
 

--- a/home/blog.xlsx
+++ b/home/blog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B75CCA3-3B63-4336-A2DE-F16B8D74EE5D}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661488A5-EB2D-4131-B6F5-1DA44416524A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
   </bookViews>
   <sheets>
     <sheet name="config_tabs" sheetId="1" r:id="rId1"/>
@@ -720,7 +720,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,6 +741,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -764,13 +770,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1200,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88D0B85-D984-4D19-B675-7655ADC2E635}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
@@ -1466,6 +1474,48 @@
       <c r="H11" t="s">
         <v>61</v>
       </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/home/blog.xlsx
+++ b/home/blog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C6B236-891F-45F6-9104-4A024CDD344C}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661488A5-EB2D-4131-B6F5-1DA44416524A}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="6" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
   </bookViews>
   <sheets>
     <sheet name="config_tabs" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="160">
   <si>
     <t>tab_key</t>
   </si>
@@ -159,19 +159,594 @@
   </si>
   <si>
     <t>allow_comments</t>
+  </si>
+  <si>
+    <t># Regras da Liga de Fantasy Basketball
+Liga de Fantasy Basketball em formato keeper, no qual os times se mantêm ao final de uma temporada, permanecendo o mesmo elenco por vários anos, podendo ser alterado apenas por dispensas, trocas, draft e contratações de Free Agents. São 14 times se enfrentando em 39 jogos na regular season, e os 8 primeiros se classificam para os playoffs.
+## 0. Configurações Gerais
+- Neste fantasy, você monta o seu elenco inicial através de um draft de balizamento, realizado na temporada de abertura da liga.
+- Durante a temporada, em cada semana de jogos, você escala o seu time com 6 titulares, sendo um de cada posição (PG, SG, SF, PF e C) e um 6th man, que pode ser de qualquer posição.
+- Além dos titulares, escala-se 6 reservas, sendo um de cada posição e um 6th man.
+- Em cada semana, todas as equipes enfrentam outros 3 times.
+- Os critérios utilizados nos jogos serão os números produzidos pelos jogadores durante a semana na NBA: pontos, assistências, rebotes, steals, blocks, bolas de 3 e turnovers.
+- A soma dos resultados obtidos pelos titulares em cada quesito será a pontuação final do time.
+- Vence o jogo o time que vencer o maior número desses 7 quesitos.
+- Os critérios de desempate serão, nesta ordem: maior eficiência naquele jogo, mais pontos, mais rebotes e assim sucessivamente. Em caso de empate em todos os critérios, haverá sorteio.
+- É obrigatória a escalação semanal de todos os times. Cada GM deve postar sua escalação no tópico de escalações do VK.
+- Se o jogador escalado não entrar em quadra por qualquer motivo, será utilizado um reserva da mesma posição.
+- A escalação poderá ser feita até 1 hora antes do início das partidas de cada semana.
+- Caso o GM não envie a escalação, será utilizada a escalação da semana anterior.
+- Duas semanas sem envio não justificado geram notificação ao GM. Em caso de repetição, haverá WO.
+## 1. Elenco
+- Ao início da temporada regular, cada elenco do time principal deve conter entre 12 e 15 jogadores.
+- O elenco da D-League deve conter entre 0 e 5 jogadores.
+- O elenco principal deve ter pelo menos 2 jogadores de cada posição: PG, SG, SF, PF e C.
+- Na D-League não existem restrições sobre posições, porém esses jogadores não contam para o elenco principal.
+- A quantidade de jogadores no elenco principal não precisa ser respeitada durante os períodos de intertemporada.
+- Nos períodos sem jogos, os times podem ultrapassar os limites de salário e de número de jogadores, mas devem voltar à regularidade até a data limite de 7 dias antes do início da nova temporada.
+- O elenco da D-League nunca pode ultrapassar o teto salarial da D-League.
+- A não adequação antes da temporada regular, ou a permanência fora das regras durante a temporada, por falta ou excesso de jogadores ou por falta de cap space, implica em derrotas por WO durante a semana em que o time estiver irregular.
+- Em caso de persistência por múltiplas semanas, o GM com excesso de jogadores terá um contrato selecionado pela gerência da liga para dispensa.
+- Já o GM com jogador a menos continuará sofrendo WO e poderá receber um jogador de salário mínimo escolhido pela liga.
+## 2. Salários, Contratos e Dispensas
+- O teto salarial do time principal será fixo em $110,000,000.
+- O teto salarial do elenco da D-League será de $14,000,000.
+### Team Option
+- No ano em que o jogador tiver Team Option, a equipe poderá optar por continuar ou não com esse jogador.
+- Caso decida liberá-lo, não haverá multa para a equipe.
+- O jogador se tornará Free Agent irrestrito.
+- O GM poderá tentar contratar esse mesmo jogador através do leilão.
+- Se o GM não responder o tópico de Team Option dentro do prazo, o jogador será desligado do time automaticamente.
+### 2.1 Dispensas
+- O número de dispensas é ilimitado.
+- Se o jogador for dispensado durante a temporada regular, ele só poderá voltar para a mesma equipe na temporada regular seguinte.
+- Se o jogador for dispensado durante a intertemporada, ele só poderá voltar para a antiga equipe na intertemporada seguinte.
+- Se após uma dispensa o time ficar fora das normas de teto salarial e de número de jogadores no elenco, a equipe terá 24 horas para se readequar.
+- Caso contrário, a readequação será feita pela gerência da liga.
+### 2.2 Multas
+- Entre $500,000 e $5,000,000, a multa será de 15% do salário anual em cada ano de contrato.
+- Entre $5,000,001 e $10,000,000, a multa será de 20% do salário anual em cada ano de contrato.
+- Entre $10,000,001 e $15,000,000, a multa será de 25% do salário anual em cada ano de contrato.
+- A partir de $15,000,001, a multa será de 30% do salário anual em cada ano de contrato.
+- Se o jogador possuir valores diferentes em seu contrato, cada multa será calculada separadamente em cada ano.
+- As multas acumuladas durante a temporada serão descontadas no espaço disponível para ofertas nos leilões de intertemporada.
+- Essas multas não têm efeito durante a temporada regular.
+### 2.3 Anistia
+- Anistia consiste na dispensa do jogador com perdão dos dividendos salariais, ou seja, o jogador é dispensado e a equipe não paga multa.
+- Cada equipe poderá anistiar 1 jogador de seu elenco.
+- Esse jogador se tornará UFA.
+- Se o jogador for anistiado durante a temporada regular, ele só poderá voltar para a antiga equipe na próxima temporada regular.
+- Se o jogador for anistiado durante a intertemporada, ele só poderá voltar para a antiga equipe na intertemporada seguinte.
+- A anistia poderá ser feita apenas 1 vez dentro de um período de 5 temporadas.
+## 3. Trocas de Jogadores e Picks
+- As trocas podem envolver jogadores e picks de draft.
+- Cada GM envolvido na troca deverá confirmá-la no tópico de trocas.
+- Após todas as confirmações, a troca é efetivada.
+- Se o jogador for trocado durante a temporada regular, ele só poderá voltar para a antiga equipe na próxima temporada regular.
+- Se o jogador for trocado durante a intertemporada, ele só poderá voltar para a antiga equipe na próxima intertemporada.
+- Se durante a temporada regular o time ultrapassar o cap ou o limite de jogadores após uma troca, a equipe terá 24 horas para se readequar.
+- Caso contrário, a readequação será feita pela gerência da liga.
+- Se uma equipe violar as regras das picks, a troca será invalidada até que os GMs acertem um acordo válido.
+- Ao início dos playoffs, estarão proibidas trocas até o fim da pós-temporada.
+## 4. Draft de Rookies e Picks
+- Cada equipe tem 2 escolhas de draft por temporada: uma de 1ª rodada e uma de 2ª rodada.
+- Uma equipe deverá escolher ao menos 1 jogador a cada 2 anos no primeiro round do draft.
+- O sorteio das picks ocorre com base na classificação final da temporada.
+- Cada contrato de rookie terá 2 anos garantidos e 2 anos de Team Option.
+- O salário dos rookies será pré-fixado conforme a rookie scale abaixo.
+| Pick | Ano 1 | Ano 2 | Ano 3 | Ano 4 |
+|------|------:|------:|------:|------:|
+| 1st pick | $9,000,000 | $9,500,000 | $10,500,000 | $11,500,000 |
+| 2nd pick | $8,000,000 | $8,500,000 | $9,250,000 | $10,000,000 |
+| 3rd pick | $7,000,000 | $7,500,000 | $8,250,000 | $9,000,000 |
+| 4th pick | $6,000,000 | $6,500,000 | $7,000,000 | $7,500,000 |
+| 5th pick | $5,000,000 | $5,500,000 | $6,000,000 | $6,500,000 |
+| 6th pick | $4,500,000 | $5,000,000 | $5,500,000 | $6,000,000 |
+| 7th pick | $4,000,000 | $4,500,000 | $5,000,000 | $5,500,000 |
+- A partir da 8th pick, cada pick diminuirá em $200,000 no salário do primeiro ano em relação à pick anterior.
+| Pick | Ano 1 | Ano 2 | Ano 3 | Ano 4 |
+|------|------:|------:|------:|------:|
+| 8th pick | $3,800,000 | $4,000,000 | $4,200,000 | $4,500,000 |
+| 9th pick | $3,600,000 | $3,800,000 | $4,000,000 | $4,300,000 |
+| 10th pick | $3,400,000 | $3,600,000 | $3,800,000 | $4,100,000 |
+- Todas as picks de 2nd round terão salários de $1,000,000 nos 4 anos de contrato.
+## 5. Leilão de Free Agents e Mudança de Posições
+### 5.1 Leilão de Temporada Regular
+- Durante a temporada regular do fantasy, jogadores sem time poderão ser contratados com contratos até o fim da temporada.
+- As ofertas deverão ser enviadas entre segunda e quinta-feira via e-mail, VK ou WhatsApp para o GM do fantasy.
+- Os resultados serão divulgados em até 24 horas após o fim das propostas.
+### 5.1.1 Requisitos para a equipe
+- A equipe deve ter ao menos 1 espaço vago no elenco para cada proposta enviada, antes do envio.
+- Deve ter espaço salarial suficiente para acomodar o valor proposto.
+- Deve propor contrato de no máximo 1 temporada.
+- A proposta mínima deve ser de $1,000,000 e a máxima de $40,000,000.
+### 5.1.2 Critérios do leilão
+- O leilão é feito às cegas.
+- O leilão se inicia a partir da segunda semana da temporada regular e vai até a penúltima semana.
+- O time com a maior proposta salarial ficará com o jogador.
+- Se 2 times enviarem a mesma melhor oferta, os empatados terão 24 horas para enviar nova proposta.
+- Em caso de novo empate, abre-se novo período de 24 horas, e assim sucessivamente.
+- Se nesse período nenhuma das equipes empatadas enviar nova proposta, o jogador volta para a lista de jogadores sem time.
+### 5.2 Leilões de Offseason
+- Ao fim de cada temporada, alguns jogadores terão seus contratos encerrados e virarão Free Agents restritos.
+- O antigo time terá a palavra final para igualar a oferta ou não.
+- A proposta do time que possuía o jogador antes de ele virar Free Agent não conta para o limite salarial do leilão.
+- O valor disponível para contratar no leilão será o teto salarial disponível naquele ano, descontadas multas acumuladas e contratos já assinados.
+- Cada time poderá contratar até 10 jogadores no leilão.
+- O tempo de contrato é de 1 a 4 temporadas.
+- Casos de renovação não contam dentro do limite de 10 contratações.
+- Somente em casos de renovação a equipe poderá passar do limite do cap, devendo se readequar antes do início da temporada seguinte.
+- O valor mínimo para lances no leilão é $1,000,000.
+- Se durante 24 horas não houver novas propostas pelo jogador, ele assinará com a equipe da proposta atual.
+- Se algum GM oferecer o contrato máximo, 40% do teto salarial da liga, isto é, $44,000,000, o jogador fica em definitivo na equipe.
+### 5.3 Lances nos Leilões de Offseason
+- Oferta máxima que qualquer jogador pode receber: $44,000,000.
+- Oferta mínima que qualquer jogador pode receber: $1,000,000.
+- Ofertas entre $1,000,000 e $3,000,000 devem ter 1 a 3 anos de duração.
+- Ofertas entre $3,100,000 e $9,900,000 devem ter de 1 a 4 anos de duração.
+- Ofertas entre $10,000,000 e $19,900,000 devem ter duração mínima de 2 anos.
+- Ofertas a partir de $20,000,000 devem ter 3 ou 4 anos de duração.
+- As ofertas devem ser maiores que a anterior em múltiplos inteiros de $500,000.
+## 5.4 Mudança de Posições
+- Se o jogador atuou 30% da última temporada em determinada posição, com base no Basketball Reference, ele poderá jogar naquela posição.
+- Ao final de cada temporada, será disponibilizada uma lista com os jogadores que poderão modificar a posição.
+- Serão aceitas propostas de adequação da lista, desde que estejam de acordo com a referência utilizada.
+## 6. D-League
+- As equipes poderão manter parte de seus jogadores na D-League respeitando as condições abaixo.
+- Somente jogadores que ainda não finalizaram sua 3ª temporada na NBA podem ficar na D-League.
+- O elenco da D-League pode ter de 0 a 5 jogadores.
+- O teto salarial da D-League será de $14,000,000.
+- A qualquer momento na temporada, o GM poderá enviar jogadores da D-League para o elenco principal e vice-versa, desde que haja vagas e espaço na folha salarial.
+- Os jogadores da D-League poderão ser envolvidos livremente em trades.
+- Jogadores movidos para a D-League após a segunda-feira só terão efeito a partir da quinta-feira, para evitar conflito com propostas do leilão.
+- Não há regras sobre posições na D-League.
+## 7. Escalação
+A escalação de cada time é válida para 3 jogos por semana, sem poder sofrer alterações, e deve ter a seguinte estrutura:
+### Titulares
+- PG
+- SG
+- SF
+- PF
+- C
+- 6th Man
+### Reservas
+- PG
+- SG
+- SF
+- PF
+- C
+- 6th Man
+- O 6th man pode ser um jogador de qualquer posição.
+- Cada jogador pode estar em no máximo 2 posições considerando titulares e reservas.
+- Na escalação titular não pode haver repetições.
+- Se o time na NBA jogar 2 vezes na semana, as stats do jogo 2 se repetem no jogo 3.
+- Se o time na NBA jogar 1 vez na semana, as stats se repetem nas 3 partidas do fantasy.
+- Se o time na NBA não jogar durante a semana, o jogador escalado ficará de fora e entrará o reserva.
+## 8. Classificação e Playoffs
+- 14 times jogam todos contra todos 3 vezes, totalizando 39 jogos.
+- Os 8 primeiros se classificam aos playoffs.
+- As séries serão melhor de 5 jogos até a final.
+- Cada fase dos playoffs começará numa data específica, e os jogos usados para contagem dos critérios serão os 5 primeiros jogos de cada time da NBA dentro daquele período.
+- A final será dividida em 2 semanas, a primeira com 3 jogos e a segunda com 2 jogos, com possibilidade de mudança de escalação para a segunda semana.
+### Quartas de final
+- [A] Primeiro x Oitavo
+- [B] Segundo x Sétimo
+- [C] Terceiro x Sexto
+- [D] Quarto x Quinto
+### Semifinais
+- [E] Vencedor de A x Vencedor de D
+- [F] Vencedor de B x Vencedor de C
+### Final da Liga
+- Vencedor de E x Vencedor de F
+### Critérios de desempate na classificação da regular season
+**Empate entre 2 times**
+- Confronto direto.
+- Média de eficiência na temporada.
+- Número de vitórias contra os times do top 8.
+- Número de quesitos vencidos na temporada.
+- Sorteio.
+**Empate entre 3 ou mais times**
+- Número de vitórias nos confrontos envolvendo os times empatados.
+- Média de eficiência na temporada.
+- Número de vitórias contra os times do top 8.
+- Número de quesitos vencidos na temporada.
+- Sorteio.</t>
+  </si>
+  <si>
+    <t>r1</t>
+  </si>
+  <si>
+    <t>Regras 2026-27</t>
+  </si>
+  <si>
+    <t>Filipe</t>
+  </si>
+  <si>
+    <t>e1t2627</t>
+  </si>
+  <si>
+    <t>e2t2627</t>
+  </si>
+  <si>
+    <t>e3t2627</t>
+  </si>
+  <si>
+    <t>e4t2627</t>
+  </si>
+  <si>
+    <t>e5t2627</t>
+  </si>
+  <si>
+    <t>e6t2627</t>
+  </si>
+  <si>
+    <t>e7t2627</t>
+  </si>
+  <si>
+    <t>Mudanca de Posicoes</t>
+  </si>
+  <si>
+    <t>Team Option</t>
+  </si>
+  <si>
+    <t>Mudanca de Regras</t>
+  </si>
+  <si>
+    <t>Votacao de Regras</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Inicio da temporada</t>
+  </si>
+  <si>
+    <t>Playoffs</t>
+  </si>
+  <si>
+    <t>e8t2627</t>
+  </si>
+  <si>
+    <t>Realizado</t>
+  </si>
+  <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
+    <t>Aguardando</t>
+  </si>
+  <si>
+    <t>Depende do calendario oficial</t>
+  </si>
+  <si>
+    <t>26-27</t>
+  </si>
+  <si>
+    <t>Contratos</t>
+  </si>
+  <si>
+    <t>Regras</t>
+  </si>
+  <si>
+    <t>Leilao</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>Fim das trocas</t>
+  </si>
+  <si>
+    <t>Trocas</t>
+  </si>
+  <si>
+    <t>Três semanas antes do fim da temporada</t>
+  </si>
+  <si>
+    <t>e9t2627</t>
+  </si>
+  <si>
+    <t>e10t2627</t>
+  </si>
+  <si>
+    <t>Três semanas depois do inicio da temporada</t>
+  </si>
+  <si>
+    <t>jogos</t>
+  </si>
+  <si>
+    <t>links</t>
+  </si>
+  <si>
+    <t>l01</t>
+  </si>
+  <si>
+    <t>l02</t>
+  </si>
+  <si>
+    <t>l03</t>
+  </si>
+  <si>
+    <t>l04</t>
+  </si>
+  <si>
+    <t>l05</t>
+  </si>
+  <si>
+    <t>l06</t>
+  </si>
+  <si>
+    <t>l07</t>
+  </si>
+  <si>
+    <t>l08</t>
+  </si>
+  <si>
+    <t>l09</t>
+  </si>
+  <si>
+    <t>l10</t>
+  </si>
+  <si>
+    <t>l11</t>
+  </si>
+  <si>
+    <t>l12</t>
+  </si>
+  <si>
+    <t>l13</t>
+  </si>
+  <si>
+    <t>l14</t>
+  </si>
+  <si>
+    <t>l15</t>
+  </si>
+  <si>
+    <t>l16</t>
+  </si>
+  <si>
+    <t>l17</t>
+  </si>
+  <si>
+    <t>https://keepernba.streamlit.app/</t>
+  </si>
+  <si>
+    <t>pagina</t>
+  </si>
+  <si>
+    <t>página do fantasy</t>
+  </si>
+  <si>
+    <t>Padrão</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1KqIYAMizS7WNIbJXo6Lrle0lDWP1gvjPOEvm-KSj_5M/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Escalacao Padrão - Para todos editarem suas escalacoes semanalmente</t>
+  </si>
+  <si>
+    <t>Pre Season 1</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1PKz9jPsnkaemsrcfa4MAVxdS2FSvLZy3C-KhyeQkM0U/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Jogo 1 da Preseason</t>
+  </si>
+  <si>
+    <t>Jogo 2 da Preseason</t>
+  </si>
+  <si>
+    <t>Pre Season 2</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1RXlz9Xob-9LLEDgAIwHjMysaYpanNqit7m-Dh2BuxJs/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>Jogo 1 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 2 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 3 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 4 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 5 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 6 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 7 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 8 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 9 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 10 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 11 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 12 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>Jogo 13 - Temporada 26/27</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/18W8lv2YB4l5fTdtlZ4XRlFRazdmTumJMDwXXly_tpTg/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1wRaVHoT9s8wOav-gKqMe1DTkknb_4cthJj4RKU2HoaM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/18SwibH99E_Crb-pKSWfmjg0mRb9sRq8bRUjoyC0UPzU/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1VOT_9qme4yOtUn7gTMuXD5gUZIyFteDE44ro2pHLVFg/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1yrxI0tprMeHsfenGTb4k634T8J3hqh9mM6X3BS_Jp1w/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1O-DBGgH97ML9R0VZsJ-g1n8InDWd_s6e36CosxYQX1M/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1JLcZ-ulfMhjZ2dxuV49HGsCkSK77LoijaPvdFldI2Fw/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1Mi_0bBQN-r3vR3cNnVos3dZolLINHXZ5-SyI_v-m8zA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1k1nsW_OTJLcub2uI96PFD2NS6iaXF0tUpQeF9Q28YEo/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1IbvR62VxxjKDJplVXwtQJ5ctFSg0-j_YldA72NvEei0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1RRwvkrBm8WkBq9jYe1RkUfyCKkTkMa_Eps7NpdtmKzc/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/17H6QAxOUbGdGnFk39oSecTgNeuI_pYYu1MMI1ubQ9PI/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1PbO2jV6lLXgEH53PqUiZFjxOtayMbdYNTCmisdc7NhM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>A.J. Dybantsa</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>Cameron Boozer</t>
+  </si>
+  <si>
+    <t>Darryn Peterson</t>
+  </si>
+  <si>
+    <t>Darius Acuff</t>
+  </si>
+  <si>
+    <t>Kingston Flemings</t>
+  </si>
+  <si>
+    <t>Mikel Brown Jr.</t>
+  </si>
+  <si>
+    <t>Hannes Steinbach</t>
+  </si>
+  <si>
+    <t>Keaton Wagler</t>
+  </si>
+  <si>
+    <t>Morez Johnson Jr.</t>
+  </si>
+  <si>
+    <t>Brayden Burries</t>
+  </si>
+  <si>
+    <t>Aday Mara</t>
+  </si>
+  <si>
+    <t>Yaxel Lendeborg</t>
+  </si>
+  <si>
+    <t>Cameron Carr</t>
+  </si>
+  <si>
+    <t>Nate Ament</t>
+  </si>
+  <si>
+    <t>Daylin Swain</t>
+  </si>
+  <si>
+    <t>Ebuka Okorie</t>
+  </si>
+  <si>
+    <t>Allen Graves</t>
+  </si>
+  <si>
+    <t>Labaron Phillon</t>
+  </si>
+  <si>
+    <t>Meleek Thomas</t>
+  </si>
+  <si>
+    <t>Bruce Thornton</t>
+  </si>
+  <si>
+    <t>Henry Veesar</t>
+  </si>
+  <si>
+    <t>Sergio De Larrea</t>
+  </si>
+  <si>
+    <t>Bennett Stirtz</t>
+  </si>
+  <si>
+    <t>Chris Cenac Jr.</t>
+  </si>
+  <si>
+    <t>Zuby Ejiofor</t>
+  </si>
+  <si>
+    <t>Christian Anderson Jr.</t>
+  </si>
+  <si>
+    <t>Karim López</t>
+  </si>
+  <si>
+    <t>Drafted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,13 +766,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -211,6 +795,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B9A42A-589F-4B50-8669-074FEDFFFE7B}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -590,6 +1178,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46220</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -597,8 +1208,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88D0B85-D984-4D19-B675-7655ADC2E635}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -626,14 +1242,290 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46157</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46158</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46188</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46204</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46222</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46223</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46249</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46401</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46328</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46384</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46384</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46384</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46405</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46436</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="4"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84E0651-47D6-4C27-8279-ADF7176CE05C}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -644,7 +1536,7 @@
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
     <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -678,6 +1570,818 @@
       </c>
       <c r="J1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2">
+        <v>417</v>
+      </c>
+      <c r="I2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3">
+        <v>418</v>
+      </c>
+      <c r="I3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4">
+        <v>419</v>
+      </c>
+      <c r="I4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5">
+        <v>420</v>
+      </c>
+      <c r="I5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6">
+        <v>421</v>
+      </c>
+      <c r="I6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7">
+        <v>422</v>
+      </c>
+      <c r="I7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8">
+        <v>423</v>
+      </c>
+      <c r="I8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9">
+        <v>424</v>
+      </c>
+      <c r="I9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10">
+        <v>425</v>
+      </c>
+      <c r="I10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11">
+        <v>426</v>
+      </c>
+      <c r="I11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12">
+        <v>427</v>
+      </c>
+      <c r="I12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13">
+        <v>428</v>
+      </c>
+      <c r="I13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14">
+        <v>429</v>
+      </c>
+      <c r="I14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>144</v>
+      </c>
+      <c r="H15">
+        <v>430</v>
+      </c>
+      <c r="I15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16">
+        <v>431</v>
+      </c>
+      <c r="I16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17">
+        <v>432</v>
+      </c>
+      <c r="I17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18">
+        <v>433</v>
+      </c>
+      <c r="I18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19">
+        <v>434</v>
+      </c>
+      <c r="I19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20">
+        <v>435</v>
+      </c>
+      <c r="I20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21">
+        <v>436</v>
+      </c>
+      <c r="I21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22">
+        <v>437</v>
+      </c>
+      <c r="I22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23">
+        <v>438</v>
+      </c>
+      <c r="I23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24">
+        <v>439</v>
+      </c>
+      <c r="I24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25">
+        <v>440</v>
+      </c>
+      <c r="I25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26">
+        <v>441</v>
+      </c>
+      <c r="I26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27">
+        <v>442</v>
+      </c>
+      <c r="I27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28">
+        <v>443</v>
+      </c>
+      <c r="I28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29">
+        <v>444</v>
+      </c>
+      <c r="I29" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -687,9 +2391,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CCF4C6-E00D-4D0E-AC8F-5C36E1B21F35}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -716,8 +2422,420 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{D61EF50B-4C43-4162-BD20-9054571CE03F}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{1AA19000-A973-40D3-B160-9F4C454BA7BB}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{AA736724-C129-48E7-8A87-525D908E636E}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{8B10550E-32EE-48CD-ADF4-01162CF1ED0A}"/>
+    <hyperlink ref="D18" r:id="rId5" xr:uid="{8D5DF31B-2F19-47C6-AB9C-F8070017BA6E}"/>
+    <hyperlink ref="D17" r:id="rId6" xr:uid="{4F8A4F6D-D241-46EE-9657-978B55F724BE}"/>
+    <hyperlink ref="D16" r:id="rId7" xr:uid="{EF00FB91-201B-44FF-840F-20A8B8CBA11C}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{5C48C246-1A04-45F7-8463-B57B0697266F}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{BF4358BF-A78C-4BDA-B97C-A221B624B2BA}"/>
+    <hyperlink ref="D13" r:id="rId10" xr:uid="{933A162F-8C8F-4D2C-A06B-38E976979870}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{DA80FD7E-54B4-4FBA-925A-0A9237FCC767}"/>
+    <hyperlink ref="D11" r:id="rId12" xr:uid="{3C5819DB-8592-4354-8E80-B0F350F85237}"/>
+    <hyperlink ref="D9" r:id="rId13" xr:uid="{39BFEB7B-51AB-4E9C-8DF8-75C45DD71C52}"/>
+    <hyperlink ref="D8" r:id="rId14" xr:uid="{53C03D4F-F0CB-4079-8057-D8AB5F62729D}"/>
+    <hyperlink ref="D7" r:id="rId15" xr:uid="{6ACFD238-5286-4E11-89FA-350E104B7DD2}"/>
+    <hyperlink ref="D6" r:id="rId16" xr:uid="{0CA085F1-2C0B-4103-8922-39FC61C77FDB}"/>
+    <hyperlink ref="D10" r:id="rId17" xr:uid="{F512397F-5E3F-4041-9AF2-E3F1A00E1CAF}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
 
